--- a/output/pdf_financials_xlsx/NAU.xlsx
+++ b/output/pdf_financials_xlsx/NAU.xlsx
@@ -5842,19 +5842,19 @@
         <v>3.347407</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.16006</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.477172</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.442566</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.252174</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.929879</v>
       </c>
     </row>
     <row r="93">
@@ -7245,10 +7245,10 @@
         <v>-2.116071</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.691124</v>
+        <v>-1.416296</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>3.39224</v>
+        <v>-0.105516</v>
       </c>
     </row>
     <row r="119">
@@ -10058,7 +10058,11 @@
           <t>Reserve 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11056,7 +11060,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11998,7 +12006,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -18568,7 +18580,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NAU.xlsx
+++ b/output/pdf_financials_xlsx/NAU.xlsx
@@ -1083,46 +1083,46 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.039505</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.028142</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019081</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011172</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.005546</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003059</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000359</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000447</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000475</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.009561999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.008633999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.019976</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.022629</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.046359</v>
       </c>
     </row>
     <row r="13">
@@ -2034,28 +2034,28 @@
         <v>-0.291581</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.668691</v>
+        <v>-1.708196</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.356193</v>
+        <v>-0.384335</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.176874</v>
+        <v>-0.195955</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.071437</v>
+        <v>-0.082609</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.198027</v>
+        <v>-0.203573</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.171349</v>
+        <v>-0.174408</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.142871</v>
+        <v>-0.14323</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.031768</v>
+        <v>-0.032215</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.894392</v>
+        <v>-2.903954</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.529075</v>
+        <v>-2.537709</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.630066</v>
+        <v>-2.650042</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.664947</v>
+        <v>-3.687576</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-8.751758000000001</v>
+        <v>-8.798117</v>
       </c>
     </row>
     <row r="28">
@@ -2150,28 +2150,28 @@
         <v>-0.291452</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.666453</v>
+        <v>-1.705958</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.351502</v>
+        <v>-0.379644</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.17191</v>
+        <v>-0.190991</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.066691</v>
+        <v>-0.077863</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.194492</v>
+        <v>-0.200038</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.168462</v>
+        <v>-0.171521</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.139984</v>
+        <v>-0.140343</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.028881</v>
+        <v>-0.029328</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2179,19 +2179,19 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.885252</v>
+        <v>-2.894814</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.466621</v>
+        <v>-2.475255</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.562153</v>
+        <v>-2.582129</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.596067</v>
+        <v>-3.618696</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-8.681533999999999</v>
+        <v>-8.727893</v>
       </c>
     </row>
     <row r="30">
@@ -2476,10 +2476,10 @@
         <v>0.00131</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.757793</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.495565</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.15152</v>
@@ -2590,10 +2590,10 @@
         <v>0.00131</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.757793</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.495565</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.15152</v>
@@ -3274,10 +3274,10 @@
         <v>0.010629</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.779131</v>
+        <v>0.021338</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.774831</v>
+        <v>0.279266</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.017776</v>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -44958,7 +44958,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -48992,7 +48992,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -49516,7 +49516,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -51724,7 +51724,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">

--- a/output/pdf_financials_xlsx/NAU.xlsx
+++ b/output/pdf_financials_xlsx/NAU.xlsx
@@ -6882,16 +6882,16 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.00059</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.00063</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -7348,10 +7348,10 @@
         <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>6.885415</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="3" t="n">
         <v>0</v>
@@ -24574,7 +24574,11 @@
           <t>Issuance of common shares, net of issuance cost</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -31684,7 +31688,11 @@
           <t>Proceeds on disposition of property and equipment 4</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33170,7 +33178,11 @@
           <t>Proceeds on disposition of property and equipment 4</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -34796,7 +34808,11 @@
           <t>Proceeds on disposition of property and equipment (note 3)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NAU.xlsx
+++ b/output/pdf_financials_xlsx/NAU.xlsx
@@ -1317,10 +1317,10 @@
         <v>-0.356193</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.176874</v>
+        <v>-0.466116</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.071437</v>
+        <v>-0.300723</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-0.198027</v>
@@ -1376,10 +1376,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>0.289242</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>0.229286</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -2040,10 +2040,10 @@
         <v>-0.384335</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.195955</v>
+        <v>-0.485197</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.082609</v>
+        <v>-0.311895</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.203573</v>
@@ -2156,10 +2156,10 @@
         <v>-0.379644</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.190991</v>
+        <v>-0.480233</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.077863</v>
+        <v>-0.307149</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.200038</v>
@@ -2302,10 +2302,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-62.05365188064773</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-76.24491641809905</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -6268,16 +6268,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.015216</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004967</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.123871</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.048149</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.067272</v>
@@ -6286,10 +6286,10 @@
         <v>-0.003154</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.03848</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002839</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
@@ -6561,10 +6561,10 @@
         <v>-0.034995</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.008784999999999999</v>
+        <v>0.029695</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.005736</v>
+        <v>0.002897</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0.009508000000000001</v>
@@ -6766,49 +6766,49 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.000106</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.000162</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.00014</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000757</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.000815</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.003024</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.022462</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.019704</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.221236</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.548702</v>
       </c>
     </row>
     <row r="111">
@@ -17126,7 +17126,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -20678,7 +20682,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -29864,7 +29872,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -29950,7 +29962,11 @@
           <t>Deferred tax recovery 10</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31126,7 +31142,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -31310,7 +31330,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -34238,7 +34262,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -35466,7 +35494,11 @@
           <t>Accretion expense (note 7)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -35658,7 +35690,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -50880,7 +50916,11 @@
           <t>Net loss before deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
